--- a/backend/Master.xlsx
+++ b/backend/Master.xlsx
@@ -1646,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:LU61"/>
+  <dimension ref="A2:LX61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="9" customWidth="1" style="16" min="1" max="2"/>
@@ -2825,6 +2825,21 @@
           <t>1122312</t>
         </is>
       </c>
+      <c r="LV6" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="LW6" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="LX6" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="34" t="n"/>
@@ -4476,6 +4491,21 @@
           <t>TEST 2</t>
         </is>
       </c>
+      <c r="LV7" t="inlineStr">
+        <is>
+          <t>5666666</t>
+        </is>
+      </c>
+      <c r="LW7" t="inlineStr">
+        <is>
+          <t>TEST3</t>
+        </is>
+      </c>
+      <c r="LX7" t="inlineStr">
+        <is>
+          <t>123456789</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="34" t="n"/>
@@ -4490,7 +4520,7 @@
         </is>
       </c>
       <c r="E8" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="27" t="n">
         <v>2.95</v>
@@ -4511,13 +4541,13 @@
         <v>5</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="27" t="n">
         <v>2</v>
       </c>
       <c r="N8" s="27" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="O8" s="27" t="n">
         <v>2</v>
@@ -4565,22 +4595,22 @@
         <v>0</v>
       </c>
       <c r="AD8" s="27" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="27" t="n">
         <v>2.25</v>
       </c>
       <c r="AF8" s="27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG8" s="27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH8" s="27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" s="27" t="n">
         <v>10</v>
@@ -4628,10 +4658,10 @@
         <v>7.2</v>
       </c>
       <c r="AY8" s="27" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="AZ8" s="27" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="BA8" s="27" t="n">
         <v>10</v>
@@ -4973,7 +5003,7 @@
         <v>3.95</v>
       </c>
       <c r="FJ8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FK8" s="23" t="n">
         <v>1</v>
@@ -5006,7 +5036,7 @@
         <v>2</v>
       </c>
       <c r="FU8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="FV8" s="23" t="n">
         <v>5</v>
@@ -5027,7 +5057,7 @@
         <v>1</v>
       </c>
       <c r="GB8" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="GC8" s="23" t="n">
         <v>5</v>
@@ -5042,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="GG8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GH8" s="23" t="n">
         <v>5</v>
@@ -5066,28 +5096,28 @@
         <v>5</v>
       </c>
       <c r="GO8" s="23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="GP8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GQ8" s="23" t="n">
         <v>2</v>
       </c>
       <c r="GR8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GS8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GT8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GU8" s="23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="GV8" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="GW8" s="27" t="n">
         <v>3</v>
@@ -5474,6 +5504,15 @@
         <v>4</v>
       </c>
       <c r="LU8" t="n">
+        <v>4</v>
+      </c>
+      <c r="LV8" t="n">
+        <v>2</v>
+      </c>
+      <c r="LW8" t="n">
+        <v>3</v>
+      </c>
+      <c r="LX8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6479,6 +6518,15 @@
       </c>
       <c r="LU9" t="n">
         <v>-0.0575</v>
+      </c>
+      <c r="LV9" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="LW9" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="LX9" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
@@ -7480,6 +7528,15 @@
       <c r="LU10" t="n">
         <v>-0.045</v>
       </c>
+      <c r="LV10" t="n">
+        <v>-0.3375</v>
+      </c>
+      <c r="LW10" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="LX10" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="40" t="n"/>
@@ -8480,6 +8537,15 @@
       <c r="LU11" t="n">
         <v>0.415</v>
       </c>
+      <c r="LV11" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="LW11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="LX11" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="41" t="n"/>
@@ -9480,6 +9546,15 @@
       <c r="LU12" t="n">
         <v>0.5075</v>
       </c>
+      <c r="LV12" t="n">
+        <v>0.9065</v>
+      </c>
+      <c r="LW12" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="LX12" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="34" t="inlineStr">
@@ -10483,6 +10558,15 @@
       </c>
       <c r="LU13" t="n">
         <v>0.18</v>
+      </c>
+      <c r="LV13" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="LW13" t="n">
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="LX13" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="14">
@@ -11484,6 +11568,15 @@
       <c r="LU14" t="n">
         <v>0.1625</v>
       </c>
+      <c r="LV14" t="n">
+        <v>-0.0735</v>
+      </c>
+      <c r="LW14" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="LX14" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="40" t="n"/>
@@ -12484,6 +12577,15 @@
       <c r="LU15" t="n">
         <v>0.545</v>
       </c>
+      <c r="LV15" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="LW15" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="LX15" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="41" t="n"/>
@@ -13484,6 +13586,15 @@
       <c r="LU16" t="n">
         <v>0.625</v>
       </c>
+      <c r="LV16" t="n">
+        <v>1.2695</v>
+      </c>
+      <c r="LW16" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="LX16" t="n">
+        <v>1.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="34" t="n"/>
@@ -14484,6 +14595,15 @@
       <c r="LU17" t="n">
         <v>104.8925</v>
       </c>
+      <c r="LV17" t="n">
+        <v>96.77</v>
+      </c>
+      <c r="LW17" t="n">
+        <v>103.9067</v>
+      </c>
+      <c r="LX17" t="n">
+        <v>88</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="34" t="inlineStr">
@@ -15953,6 +16073,12 @@
       </c>
       <c r="LU18" t="n">
         <v>-0.175</v>
+      </c>
+      <c r="LV18" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="LW18" t="n">
+        <v>-0.2767</v>
       </c>
     </row>
     <row r="19">
@@ -17420,6 +17546,12 @@
       <c r="LU19" t="n">
         <v>-0.2525</v>
       </c>
+      <c r="LV19" t="n">
+        <v>-0.281</v>
+      </c>
+      <c r="LW19" t="n">
+        <v>-0.1133</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="40" t="n"/>
@@ -18886,6 +19018,12 @@
       <c r="LU20" t="n">
         <v>-0.53</v>
       </c>
+      <c r="LV20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="LW20" t="n">
+        <v>-0.8667</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="40" t="n"/>
@@ -20352,6 +20490,12 @@
       <c r="LU21" t="n">
         <v>1.125</v>
       </c>
+      <c r="LV21" t="n">
+        <v>0.8375</v>
+      </c>
+      <c r="LW21" t="n">
+        <v>0.8933</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="41" t="n"/>
@@ -21818,6 +21962,12 @@
       <c r="LU22" t="n">
         <v>99.77249999999999</v>
       </c>
+      <c r="LV22" t="n">
+        <v>97.886</v>
+      </c>
+      <c r="LW22" t="n">
+        <v>97.70999999999999</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="34" t="inlineStr">
@@ -84459,82 +84609,182 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="EU61" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="EV61" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="FJ61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="FQ61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="FR61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="FU61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GB61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GF61" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="GG61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GO61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GP61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GR61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="GS61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GT61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GU61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="GV61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="LT61" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="EU61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="EV61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="FQ61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="FR61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="GF61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="GO61" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="LT61" t="inlineStr">
+      <c r="LU61" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="LU61" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
+      <c r="LV61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="LW61" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="LX61" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
